--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/NEW_MEXICO_2022.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/NEW_MEXICO_2022.xlsx
@@ -445,7 +445,7 @@
         <v>3</v>
       </c>
       <c r="D5">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="6">
@@ -661,7 +661,7 @@
         <v>3</v>
       </c>
       <c r="D17">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="18">
@@ -751,7 +751,7 @@
         <v>3</v>
       </c>
       <c r="D22">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="23">
@@ -1471,7 +1471,7 @@
         <v>3</v>
       </c>
       <c r="D62">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="63">
@@ -1705,7 +1705,7 @@
         <v>3</v>
       </c>
       <c r="D75">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="76">
@@ -1921,7 +1921,7 @@
         <v>3</v>
       </c>
       <c r="D87">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="88">
@@ -1975,7 +1975,7 @@
         <v>3</v>
       </c>
       <c r="D90">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="91">
@@ -1993,7 +1993,7 @@
         <v>3</v>
       </c>
       <c r="D91">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="92">
@@ -2245,7 +2245,7 @@
         <v>3</v>
       </c>
       <c r="D105">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="106">
@@ -2263,7 +2263,7 @@
         <v>3</v>
       </c>
       <c r="D106">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="107">
@@ -2389,7 +2389,7 @@
         <v>3</v>
       </c>
       <c r="D113">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="114">
@@ -2965,7 +2965,7 @@
         <v>3</v>
       </c>
       <c r="D145">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="146">
@@ -3001,7 +3001,7 @@
         <v>3</v>
       </c>
       <c r="D147">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="148">
@@ -3091,7 +3091,7 @@
         <v>3</v>
       </c>
       <c r="D152">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="153">
@@ -3181,7 +3181,7 @@
         <v>3</v>
       </c>
       <c r="D157">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="158">
@@ -3199,7 +3199,7 @@
         <v>3</v>
       </c>
       <c r="D158">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="159">
@@ -3379,7 +3379,7 @@
         <v>3</v>
       </c>
       <c r="D168">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="169">
@@ -3505,7 +3505,7 @@
         <v>3</v>
       </c>
       <c r="D175">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="176">
@@ -3685,7 +3685,7 @@
         <v>3</v>
       </c>
       <c r="D185">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="186">
@@ -3739,7 +3739,7 @@
         <v>3</v>
       </c>
       <c r="D188">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="189">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C189">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C194">
@@ -3973,7 +3973,7 @@
         <v>3</v>
       </c>
       <c r="D201">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="202">
@@ -3991,7 +3991,7 @@
         <v>3</v>
       </c>
       <c r="D202">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="203">
@@ -4117,7 +4117,7 @@
         <v>3</v>
       </c>
       <c r="D209">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="210">
@@ -4315,7 +4315,7 @@
         <v>3</v>
       </c>
       <c r="D220">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="221">
@@ -4945,7 +4945,7 @@
         <v>3</v>
       </c>
       <c r="D255">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="256">
@@ -5161,7 +5161,7 @@
         <v>3</v>
       </c>
       <c r="D267">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="268">
@@ -5197,7 +5197,7 @@
         <v>3</v>
       </c>
       <c r="D269">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="270">
@@ -5287,7 +5287,7 @@
         <v>3</v>
       </c>
       <c r="D274">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="275">
@@ -5449,7 +5449,7 @@
         <v>3</v>
       </c>
       <c r="D283">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="284">
@@ -5485,7 +5485,7 @@
         <v>3</v>
       </c>
       <c r="D285">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="286">
@@ -5629,7 +5629,7 @@
         <v>3</v>
       </c>
       <c r="D293">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="294">
@@ -5791,7 +5791,7 @@
         <v>3</v>
       </c>
       <c r="D302">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="303">
@@ -5989,7 +5989,7 @@
         <v>3</v>
       </c>
       <c r="D313">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="314">
@@ -6061,7 +6061,7 @@
         <v>3</v>
       </c>
       <c r="D317">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="318">
@@ -6475,7 +6475,7 @@
         <v>3</v>
       </c>
       <c r="D340">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="341">
@@ -6493,7 +6493,7 @@
         <v>3</v>
       </c>
       <c r="D341">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="342">
@@ -6511,7 +6511,7 @@
         <v>3</v>
       </c>
       <c r="D342">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="343">
@@ -6799,7 +6799,7 @@
         <v>3</v>
       </c>
       <c r="D358">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="359">
@@ -6889,7 +6889,7 @@
         <v>3</v>
       </c>
       <c r="D363">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="364">
@@ -7116,7 +7116,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C376">
@@ -7267,7 +7267,7 @@
         <v>3</v>
       </c>
       <c r="D384">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="385">
@@ -7447,7 +7447,7 @@
         <v>3</v>
       </c>
       <c r="D394">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="395">
@@ -7699,7 +7699,7 @@
         <v>3</v>
       </c>
       <c r="D408">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="409">
@@ -7879,7 +7879,7 @@
         <v>3</v>
       </c>
       <c r="D418">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="419">
@@ -8311,7 +8311,7 @@
         <v>3</v>
       </c>
       <c r="D442">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="443">
@@ -8437,7 +8437,7 @@
         <v>3</v>
       </c>
       <c r="D449">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="450">
@@ -8905,7 +8905,7 @@
         <v>3</v>
       </c>
       <c r="D475">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="476">
@@ -9031,7 +9031,7 @@
         <v>3</v>
       </c>
       <c r="D482">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="483">
@@ -9085,7 +9085,7 @@
         <v>3</v>
       </c>
       <c r="D485">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="486">
@@ -9391,7 +9391,7 @@
         <v>3</v>
       </c>
       <c r="D502">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="503">
@@ -9967,7 +9967,7 @@
         <v>3</v>
       </c>
       <c r="D534">
-        <v>0.0009708737864077669</v>
+        <v>0.0009708737864077668</v>
       </c>
     </row>
     <row r="535">
